--- a/usertest/veteran/r16/dl/rt-sample-archive.xlsx
+++ b/usertest/veteran/r16/dl/rt-sample-archive.xlsx
@@ -1263,7 +1263,7 @@
     <t>承認</t>
   </si>
   <si>
-    <t>2026-10-21 18:04</t>
+    <t>2026-10-21 18:11</t>
   </si>
   <si>
     <t>山田</t>
